--- a/LA5/performanceDataPrimeCounter.xlsx
+++ b/LA5/performanceDataPrimeCounter.xlsx
@@ -8,18 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\crawfordd1\git\Labs\LA5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38568AE5-E257-4F52-8129-EBCB41D59935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4987DA-4386-451C-BB6E-B88A984EFCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6390" windowWidth="16440" windowHeight="28320" firstSheet="1" activeTab="1" xr2:uid="{8F8FE5A9-64AB-4105-B159-B1A00C2AFACE}"/>
+    <workbookView xWindow="6300" yWindow="-5940" windowWidth="16440" windowHeight="28320" firstSheet="1" activeTab="1" xr2:uid="{8F8FE5A9-64AB-4105-B159-B1A00C2AFACE}"/>
   </bookViews>
   <sheets>
-    <sheet name="first unique balance" sheetId="1" r:id="rId1"/>
-    <sheet name="logarithmic scale" sheetId="2" r:id="rId2"/>
-    <sheet name="naive vs pesudoballance" sheetId="3" r:id="rId3"/>
+    <sheet name="logarithmic scale" sheetId="2" r:id="rId1"/>
+    <sheet name="naive vs pesudoballance" sheetId="3" r:id="rId2"/>
+    <sheet name="first unique balance" sheetId="1" r:id="rId3"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'logarithmic scale'!$A$3</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'logarithmic scale'!$B$2:$H$2</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'logarithmic scale'!$B$3:$H$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
   <si>
     <t xml:space="preserve">Number of Ranks: </t>
   </si>
@@ -62,6 +67,18 @@
   </si>
   <si>
     <t>n/(numrank*10)</t>
+  </si>
+  <si>
+    <t>Naïve Chunk Size</t>
+  </si>
+  <si>
+    <t>Pesudo Ballanced Chunk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naive time taken: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimized time taken: </t>
   </si>
 </sst>
 </file>
@@ -131,6 +148,2568 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Logarithmic</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Search Results</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'logarithmic scale'!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Full time taken: </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'logarithmic scale'!$B$2:$G$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'logarithmic scale'!$B$3:$G$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10.561237999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1574279999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32914399999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26278600000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25232199999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.28771799999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-94D1-416F-A369-89F0DDB6EFD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="985101391"/>
+        <c:axId val="985100431"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="985101391"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Size of Chunk (#</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> of numbers per rank</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="985100431"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="985100431"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Full</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> Time (s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="985101391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Pesudo</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Optimal Chunk Size</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t> : 50,000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'naive vs pesudoballance'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Full time taken: </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$10:$K$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$11:$K$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.4812160000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5081180000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.769787</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53296100000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.397868</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.342032</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.29220400000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.28526000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25111699999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.249556</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4733-4821-B776-1E9017E2C8A0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1033999855"/>
+        <c:axId val="1034000335"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1033999855"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rank</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1034000335"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1034000335"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1033999855"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Naive</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Chunk Size</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'naive vs pesudoballance'!$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Full time taken: </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{3971B5FE-0DEF-460B-851D-8C146E7A76F7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5F189D74-CFF9-41A1-A2BA-468BE7C04D2F}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{EA49E3B4-BF99-41A4-B17D-E5998948E681}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DF2E1C95-F1D4-48D0-B40D-70DACC28111A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A53863F2-BED8-4F13-90F7-013B677924FF}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D1A6C075-B92E-423B-932B-FFB77971C36C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{17F02ACC-1FCF-4C45-BF9C-55B3F466A870}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{10D5CD99-1801-49F1-AA04-97500AB82A8F}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E604AAFB-7312-4FE3-AEE7-708C9181C292}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F10945C8-2C6D-492D-8A36-43A865466AA0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-F255-41C0-AA10-2C552F985A56}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$3:$K$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$4:$K$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.4703660000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4894019999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97548599999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72353500000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57288700000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.47585100000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39552199999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34536899999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.31365599999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.27810200000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'naive vs pesudoballance'!$B$2:$K$2</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="10"/>
+                  <c:pt idx="0">
+                    <c:v>10000000</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>5000000</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3333333</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>2500000</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>2000000</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>1666666</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>1428571</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>1250000</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>1111111</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>1000000</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F255-41C0-AA10-2C552F985A56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1022466447"/>
+        <c:axId val="1022467407"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1022466447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rank</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1022467407"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1022467407"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1022466447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Optimal</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> vs Naive</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'naive vs pesudoballance'!$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Naive time taken: </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$15:$K$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$16:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.4703660000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4894019999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.97548599999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.72353500000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57288700000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.47585100000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39552199999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.34536899999999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.31365599999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.27810200000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-00DE-452F-ACB0-F6FAE804B9B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'naive vs pesudoballance'!$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Optimized time taken: </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$15:$K$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'naive vs pesudoballance'!$B$17:$K$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.4812160000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5081180000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.769787</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53296100000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.397868</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.342032</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.29220400000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.28526000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25111699999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.249556</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-00DE-452F-ACB0-F6FAE804B9B5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="401313023"/>
+        <c:axId val="401308703"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="401313023"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rank</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="401308703"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="401308703"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (s)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="401313023"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -212,7 +2791,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{242D90A1-5661-4BF3-B2F5-0C52C835F617}" type="CELLRANGE">
+                    <a:fld id="{67DA78EA-FEA9-489D-AA84-4EE50F1DA44E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -246,7 +2825,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A8CF3B04-E41D-4976-AB85-032E84E1A1B6}" type="CELLRANGE">
+                    <a:fld id="{5CEC161A-C37A-42F1-AECF-BFD155E5FE88}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -280,7 +2859,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CB0607B-C54B-4AA4-BE0E-5F33B3377124}" type="CELLRANGE">
+                    <a:fld id="{C79DEEE1-F525-42D6-B0C6-C4B4DE03B20B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -314,7 +2893,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DD8F7CA2-2A14-495C-8560-202DC627BFE4}" type="CELLRANGE">
+                    <a:fld id="{F2EA617C-23EC-4840-9DD0-064A035AB6A7}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -348,7 +2927,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D71077AC-C156-490C-B3CF-DBFA239A464C}" type="CELLRANGE">
+                    <a:fld id="{A098534D-E042-4A2F-80F1-AD98D48E2779}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -382,7 +2961,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2694AFA7-2B41-460C-A8A3-E18400DBB954}" type="CELLRANGE">
+                    <a:fld id="{CA17A51D-4401-474D-9F21-8AE6B81F10FB}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -416,7 +2995,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FB19D29F-80B3-4994-A72F-E80FFCB9A8C7}" type="CELLRANGE">
+                    <a:fld id="{EBFC7BD5-C0DD-4D19-BD9E-7B5610472442}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -450,7 +3029,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E42F52F7-D6C8-4205-AFC3-E10C1CABCD29}" type="CELLRANGE">
+                    <a:fld id="{B9EBAE6F-EE79-42AA-ABAC-5064A9761962}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -484,7 +3063,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{18C46FAD-12F5-4343-885B-86D32A91EDCE}" type="CELLRANGE">
+                    <a:fld id="{CDE8893B-9035-43C6-86D1-C36002DDC5F2}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -518,7 +3097,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F8E12748-2951-43A2-B076-9574A10116C4}" type="CELLRANGE">
+                    <a:fld id="{B5765125-B886-45CD-94A9-7BDF3FCBEBBA}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1035,1268 +3614,6 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'logarithmic scale'!$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Full time taken: </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'logarithmic scale'!$B$2:$H$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>10000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'logarithmic scale'!$B$3:$H$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>10.561237999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.1574279999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.32914399999999999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.26278600000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.25232199999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.28771799999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6.9726999999999997E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-94D1-416F-A369-89F0DDB6EFD9}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="985101391"/>
-        <c:axId val="985100431"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="985101391"/>
-        <c:scaling>
-          <c:logBase val="10"/>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Size of Chunk (#</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> of numbers per rank</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="985100431"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="985100431"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Full</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> Time (s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="985101391"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Full time taken: Data Marked by Rank</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'naive vs pesudoballance'!$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Full time taken: </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{296ABED8-53D6-4226-99A1-5DD9B8E2227D}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{44D9D4EA-B19C-467D-A526-8F596D799692}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000002-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{F26AE3A2-D7B7-4141-AE3A-EA20E10488B9}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000003-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{F7865B73-F3AF-4C1E-AC61-F887222DA82E}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000004-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{192034D9-00D1-4BD9-9772-9A95952A0AB0}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000005-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{E3B6B063-F746-4F33-B658-2AB6DBAC270B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000006-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{C4758B28-5D7F-4CFB-A03C-EDFDB5E9A358}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000007-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{D2B3BE54-246E-455A-B091-5E11CB126205}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000008-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="8"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{263FAC0A-B576-42AD-96D4-076AEEDE84AE}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000009-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="9"/>
-              <c:tx>
-                <c:rich>
-                  <a:bodyPr/>
-                  <a:lstStyle/>
-                  <a:p>
-                    <a:fld id="{35796A43-02FB-4BF9-A9A9-6080ED839F2D}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
-                      <a:pPr/>
-                      <a:t>[CELLRANGE]</a:t>
-                    </a:fld>
-                    <a:endParaRPr lang="en-US"/>
-                  </a:p>
-                </c:rich>
-              </c:tx>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
-                  <c15:showDataLabelsRange val="1"/>
-                </c:ext>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{0000000A-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showDataLabelsRange val="1"/>
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'naive vs pesudoballance'!$B$3:$K$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>10000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>5000000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3333333</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2500000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2000000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1666666</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1428571</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1250000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1111111</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'naive vs pesudoballance'!$B$4:$K$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>1.4703660000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4894019999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.97548599999999996</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.72353500000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.57288700000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.47585100000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.39552199999999998</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.34536899999999998</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.31365599999999999</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.27810200000000002</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-              <c15:datalabelsRange>
-                <c15:f>'naive vs pesudoballance'!$B$2:$K$2</c15:f>
-                <c15:dlblRangeCache>
-                  <c:ptCount val="10"/>
-                  <c:pt idx="0">
-                    <c:v>1</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>2</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>3</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>4</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>5</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>6</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>7</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>8</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>9</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>10</c:v>
-                  </c:pt>
-                </c15:dlblRangeCache>
-              </c15:datalabelsRange>
-            </c:ext>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B840-4A7A-95EC-2A19BC5BEC9E}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="26802495"/>
-        <c:axId val="26802975"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="26802495"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="26802975"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="26802975"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="26802495"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2417,6 +3734,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -3965,48 +5362,1039 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1533525</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>138112</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2247940-5EE2-F3AD-2CCD-A5A02C814CDA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4047,27 +6435,140 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3917F43B-C71C-E6B2-2629-6C39042DA5A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30FFD1BE-311E-3817-5834-D66FC83814B8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>538162</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>233362</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF4BF144-E729-7145-740D-D9B6768C7FEB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1533525</xdr:colOff>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>61912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="8" name="Chart 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B43E3514-3A96-4822-69A8-7C2F31ECC43F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2247940-5EE2-F3AD-2CCD-A5A02C814CDA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4508,6 +7009,629 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D3B8D8-DDB6-4306-A38C-A84D25C98110}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>10</v>
+      </c>
+      <c r="C1">
+        <v>10</v>
+      </c>
+      <c r="D1">
+        <v>10</v>
+      </c>
+      <c r="E1">
+        <v>10</v>
+      </c>
+      <c r="F1">
+        <v>10</v>
+      </c>
+      <c r="G1">
+        <v>10</v>
+      </c>
+      <c r="H1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>10000</v>
+      </c>
+      <c r="F2">
+        <v>100000</v>
+      </c>
+      <c r="G2">
+        <v>1000000</v>
+      </c>
+      <c r="H2">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>10.561237999999999</v>
+      </c>
+      <c r="C3">
+        <v>1.1574279999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.32914399999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.26278600000000002</v>
+      </c>
+      <c r="F3">
+        <v>0.25232199999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.28771799999999997</v>
+      </c>
+      <c r="H3">
+        <v>6.9726999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>664579</v>
+      </c>
+      <c r="C4">
+        <v>664579</v>
+      </c>
+      <c r="D4">
+        <v>664579</v>
+      </c>
+      <c r="E4">
+        <v>664579</v>
+      </c>
+      <c r="F4">
+        <v>664579</v>
+      </c>
+      <c r="G4">
+        <v>664579</v>
+      </c>
+      <c r="H4">
+        <v>664579</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>664579</v>
+      </c>
+      <c r="C5">
+        <v>664579</v>
+      </c>
+      <c r="D5">
+        <v>664579</v>
+      </c>
+      <c r="E5">
+        <v>664579</v>
+      </c>
+      <c r="F5">
+        <v>664579</v>
+      </c>
+      <c r="G5">
+        <v>664579</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526B55F7-CBFC-4840-860D-8D58CA4DD339}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10000000</v>
+      </c>
+      <c r="C2">
+        <v>5000000</v>
+      </c>
+      <c r="D2">
+        <v>3333333</v>
+      </c>
+      <c r="E2">
+        <v>2500000</v>
+      </c>
+      <c r="F2">
+        <v>2000000</v>
+      </c>
+      <c r="G2">
+        <v>1666666</v>
+      </c>
+      <c r="H2">
+        <v>1428571</v>
+      </c>
+      <c r="I2">
+        <v>1250000</v>
+      </c>
+      <c r="J2">
+        <v>1111111</v>
+      </c>
+      <c r="K2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>1.4703660000000001</v>
+      </c>
+      <c r="C4">
+        <v>1.4894019999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.97548599999999996</v>
+      </c>
+      <c r="E4">
+        <v>0.72353500000000004</v>
+      </c>
+      <c r="F4">
+        <v>0.57288700000000004</v>
+      </c>
+      <c r="G4">
+        <v>0.47585100000000002</v>
+      </c>
+      <c r="H4">
+        <v>0.39552199999999998</v>
+      </c>
+      <c r="I4">
+        <v>0.34536899999999998</v>
+      </c>
+      <c r="J4">
+        <v>0.31365599999999999</v>
+      </c>
+      <c r="K4">
+        <v>0.27810200000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>664579</v>
+      </c>
+      <c r="C5">
+        <v>664579</v>
+      </c>
+      <c r="D5">
+        <v>664579</v>
+      </c>
+      <c r="E5">
+        <v>664579</v>
+      </c>
+      <c r="F5">
+        <v>664579</v>
+      </c>
+      <c r="G5">
+        <v>664579</v>
+      </c>
+      <c r="H5">
+        <v>664579</v>
+      </c>
+      <c r="I5">
+        <v>664579</v>
+      </c>
+      <c r="J5">
+        <v>664579</v>
+      </c>
+      <c r="K5">
+        <v>664579</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>664579</v>
+      </c>
+      <c r="C6">
+        <v>664579</v>
+      </c>
+      <c r="D6">
+        <v>664579</v>
+      </c>
+      <c r="E6">
+        <v>664579</v>
+      </c>
+      <c r="F6">
+        <v>664579</v>
+      </c>
+      <c r="G6">
+        <v>664579</v>
+      </c>
+      <c r="H6">
+        <v>664579</v>
+      </c>
+      <c r="I6">
+        <v>664579</v>
+      </c>
+      <c r="J6">
+        <v>664579</v>
+      </c>
+      <c r="K6">
+        <v>664579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>50000</v>
+      </c>
+      <c r="C9">
+        <v>50000</v>
+      </c>
+      <c r="D9">
+        <v>50000</v>
+      </c>
+      <c r="E9">
+        <v>50000</v>
+      </c>
+      <c r="F9">
+        <v>50000</v>
+      </c>
+      <c r="G9">
+        <v>50000</v>
+      </c>
+      <c r="H9">
+        <v>50000</v>
+      </c>
+      <c r="I9">
+        <v>50000</v>
+      </c>
+      <c r="J9">
+        <v>50000</v>
+      </c>
+      <c r="K9">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
+      </c>
+      <c r="H10">
+        <v>7</v>
+      </c>
+      <c r="I10">
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>1.4812160000000001</v>
+      </c>
+      <c r="C11">
+        <v>1.5081180000000001</v>
+      </c>
+      <c r="D11">
+        <v>0.769787</v>
+      </c>
+      <c r="E11">
+        <v>0.53296100000000002</v>
+      </c>
+      <c r="F11">
+        <v>0.397868</v>
+      </c>
+      <c r="G11">
+        <v>0.342032</v>
+      </c>
+      <c r="H11">
+        <v>0.29220400000000002</v>
+      </c>
+      <c r="I11">
+        <v>0.28526000000000001</v>
+      </c>
+      <c r="J11">
+        <v>0.25111699999999998</v>
+      </c>
+      <c r="K11">
+        <v>0.249556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>664579</v>
+      </c>
+      <c r="C12">
+        <v>664579</v>
+      </c>
+      <c r="D12">
+        <v>664579</v>
+      </c>
+      <c r="E12">
+        <v>664579</v>
+      </c>
+      <c r="F12">
+        <v>664579</v>
+      </c>
+      <c r="G12">
+        <v>664579</v>
+      </c>
+      <c r="H12">
+        <v>664579</v>
+      </c>
+      <c r="I12">
+        <v>664579</v>
+      </c>
+      <c r="J12">
+        <v>664579</v>
+      </c>
+      <c r="K12">
+        <v>664579</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>664579</v>
+      </c>
+      <c r="C13">
+        <v>664579</v>
+      </c>
+      <c r="D13">
+        <v>664579</v>
+      </c>
+      <c r="E13">
+        <v>664579</v>
+      </c>
+      <c r="F13">
+        <v>664579</v>
+      </c>
+      <c r="G13">
+        <v>664579</v>
+      </c>
+      <c r="H13">
+        <v>664579</v>
+      </c>
+      <c r="I13">
+        <v>664579</v>
+      </c>
+      <c r="J13">
+        <v>664579</v>
+      </c>
+      <c r="K13">
+        <v>664579</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="J15">
+        <v>9</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>1.4703660000000001</v>
+      </c>
+      <c r="C16">
+        <v>1.4894019999999999</v>
+      </c>
+      <c r="D16">
+        <v>0.97548599999999996</v>
+      </c>
+      <c r="E16">
+        <v>0.72353500000000004</v>
+      </c>
+      <c r="F16">
+        <v>0.57288700000000004</v>
+      </c>
+      <c r="G16">
+        <v>0.47585100000000002</v>
+      </c>
+      <c r="H16">
+        <v>0.39552199999999998</v>
+      </c>
+      <c r="I16">
+        <v>0.34536899999999998</v>
+      </c>
+      <c r="J16">
+        <v>0.31365599999999999</v>
+      </c>
+      <c r="K16">
+        <v>0.27810200000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>1.4812160000000001</v>
+      </c>
+      <c r="C17">
+        <v>1.5081180000000001</v>
+      </c>
+      <c r="D17">
+        <v>0.769787</v>
+      </c>
+      <c r="E17">
+        <v>0.53296100000000002</v>
+      </c>
+      <c r="F17">
+        <v>0.397868</v>
+      </c>
+      <c r="G17">
+        <v>0.342032</v>
+      </c>
+      <c r="H17">
+        <v>0.29220400000000002</v>
+      </c>
+      <c r="I17">
+        <v>0.28526000000000001</v>
+      </c>
+      <c r="J17">
+        <v>0.25111699999999998</v>
+      </c>
+      <c r="K17">
+        <v>0.249556</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65790A7C-F61E-4708-9DBD-D9147E0C3AA3}">
   <dimension ref="A2:K9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4704,337 +7828,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D3B8D8-DDB6-4306-A38C-A84D25C98110}">
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1">
-        <v>10</v>
-      </c>
-      <c r="C1">
-        <v>10</v>
-      </c>
-      <c r="D1">
-        <v>10</v>
-      </c>
-      <c r="E1">
-        <v>10</v>
-      </c>
-      <c r="F1">
-        <v>10</v>
-      </c>
-      <c r="G1">
-        <v>10</v>
-      </c>
-      <c r="H1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>1000</v>
-      </c>
-      <c r="E2">
-        <v>10000</v>
-      </c>
-      <c r="F2">
-        <v>100000</v>
-      </c>
-      <c r="G2">
-        <v>1000000</v>
-      </c>
-      <c r="H2">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>10.561237999999999</v>
-      </c>
-      <c r="C3">
-        <v>1.1574279999999999</v>
-      </c>
-      <c r="D3">
-        <v>0.32914399999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.26278600000000002</v>
-      </c>
-      <c r="F3">
-        <v>0.25232199999999999</v>
-      </c>
-      <c r="G3">
-        <v>0.28771799999999997</v>
-      </c>
-      <c r="H3">
-        <v>6.9726999999999997E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>664579</v>
-      </c>
-      <c r="C4">
-        <v>664579</v>
-      </c>
-      <c r="D4">
-        <v>664579</v>
-      </c>
-      <c r="E4">
-        <v>664579</v>
-      </c>
-      <c r="F4">
-        <v>664579</v>
-      </c>
-      <c r="G4">
-        <v>664579</v>
-      </c>
-      <c r="H4">
-        <v>664579</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>664579</v>
-      </c>
-      <c r="C5">
-        <v>664579</v>
-      </c>
-      <c r="D5">
-        <v>664579</v>
-      </c>
-      <c r="E5">
-        <v>664579</v>
-      </c>
-      <c r="F5">
-        <v>664579</v>
-      </c>
-      <c r="G5">
-        <v>664579</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526B55F7-CBFC-4840-860D-8D58CA4DD339}">
-  <dimension ref="A2:K6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>6</v>
-      </c>
-      <c r="H2">
-        <v>7</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>10000000</v>
-      </c>
-      <c r="C3">
-        <v>5000000</v>
-      </c>
-      <c r="D3">
-        <v>3333333</v>
-      </c>
-      <c r="E3">
-        <v>2500000</v>
-      </c>
-      <c r="F3">
-        <v>2000000</v>
-      </c>
-      <c r="G3">
-        <v>1666666</v>
-      </c>
-      <c r="H3">
-        <v>1428571</v>
-      </c>
-      <c r="I3">
-        <v>1250000</v>
-      </c>
-      <c r="J3">
-        <v>1111111</v>
-      </c>
-      <c r="K3">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>1.4703660000000001</v>
-      </c>
-      <c r="C4">
-        <v>1.4894019999999999</v>
-      </c>
-      <c r="D4">
-        <v>0.97548599999999996</v>
-      </c>
-      <c r="E4">
-        <v>0.72353500000000004</v>
-      </c>
-      <c r="F4">
-        <v>0.57288700000000004</v>
-      </c>
-      <c r="G4">
-        <v>0.47585100000000002</v>
-      </c>
-      <c r="H4">
-        <v>0.39552199999999998</v>
-      </c>
-      <c r="I4">
-        <v>0.34536899999999998</v>
-      </c>
-      <c r="J4">
-        <v>0.31365599999999999</v>
-      </c>
-      <c r="K4">
-        <v>0.27810200000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>664579</v>
-      </c>
-      <c r="C5">
-        <v>664579</v>
-      </c>
-      <c r="D5">
-        <v>664579</v>
-      </c>
-      <c r="E5">
-        <v>664579</v>
-      </c>
-      <c r="F5">
-        <v>664579</v>
-      </c>
-      <c r="G5">
-        <v>664579</v>
-      </c>
-      <c r="H5">
-        <v>664579</v>
-      </c>
-      <c r="I5">
-        <v>664579</v>
-      </c>
-      <c r="J5">
-        <v>664579</v>
-      </c>
-      <c r="K5">
-        <v>664579</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>664579</v>
-      </c>
-      <c r="C6">
-        <v>664579</v>
-      </c>
-      <c r="D6">
-        <v>664579</v>
-      </c>
-      <c r="E6">
-        <v>664579</v>
-      </c>
-      <c r="F6">
-        <v>664579</v>
-      </c>
-      <c r="G6">
-        <v>664579</v>
-      </c>
-      <c r="H6">
-        <v>664579</v>
-      </c>
-      <c r="I6">
-        <v>664579</v>
-      </c>
-      <c r="J6">
-        <v>664579</v>
-      </c>
-      <c r="K6">
-        <v>664579</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>